--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -3916,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4525,7 +4525,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6034009</v>
+        <v>1106662</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4539,34 +4539,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nguyen MS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Geoffrey Gilbert9217</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>12:26.274</t>
+          <t>12:22.824</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.195</t>
+          <t>43.745</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5393539</v>
+        <v>6034009</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -4580,34 +4584,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Carsten Jensen</t>
+          <t>Nguyen MS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13:48.454</t>
+          <t>12:26.274</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>02:09.375</t>
+          <t>47.195</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6829675</v>
+        <v>1017356</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4621,34 +4625,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anders Stagsted</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Nick Overkamp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WTOS</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14:06.444</t>
+          <t>13:35.592</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>02:27.365</t>
+          <t>01:56.513</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1170121</v>
+        <v>5393539</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4662,34 +4670,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reona MTR</t>
+          <t>Carsten Jensen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14:41.692</t>
+          <t>13:48.454</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>03:02.613</t>
+          <t>02:09.375</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>718605</v>
+        <v>6829675</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4703,151 +4711,454 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>I Cant ride</t>
+          <t>Anders Stagsted</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14:43.183</t>
+          <t>14:06.444</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>03:04.104</t>
+          <t>02:27.365</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>779638</v>
+        <v>990876</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tiana Abel</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t xml:space="preserve">Pete Connor (TNP) </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14:49.694</t>
+          <t>14:28.486</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:49.407</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4651254</v>
+        <v>1170121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arjen De Jonge</t>
+          <t>Reona MTR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16:04.310</t>
+          <t>14:41.692</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>01:14.616</t>
+          <t>03:02.613</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1427961</v>
+        <v>718605</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rob Koops</t>
+          <t>I Cant ride</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
+          <t>14:43.183</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>03:04.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4177429</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F F </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L&amp;rsquo;Equipe Provence</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>13:47.095</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3084196</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>13:58.271</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>11.176</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>779638</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tiana Abel</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>14:49.694</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:02.599</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4651254</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Arjen De Jonge</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>16:04.310</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>02:17.215</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>560748</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Travis Lewis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>16:10.475</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:23.380</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>458457</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bart Van De Ven8888</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>17:45.141</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>03:58.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1427961</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rob Koops</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>18:15.800</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>03:26.106</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>04:28.705</t>
         </is>
       </c>
     </row>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W/Kg</t>
+          <t>W/kg</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W/Kg</t>
+          <t>W/kg</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W/Kg</t>
+          <t>W/kg</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>W/Kg</t>
+          <t>W/kg</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,21 +567,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6784336</v>
+        <v>7533529</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -612,46 +612,353 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>6627918</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Liam Mckeever</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08:26.409</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>01:11.871</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7799511</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08:01.945</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5186335</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>08:37.040</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35.095</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6784336</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Paul Fisk (TNP)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08:48.706</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>46.761</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>5609162</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Alan Robertson</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Team Not Pogi</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>09:00.919</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12.213</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>58.974</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7943676</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ed Henry</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>09:24.744</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>01:22.799</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>02:02.674</t>
         </is>
       </c>
     </row>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,15 +504,11 @@
           <t>06:48.434</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="G2" t="n">
+        <v>355</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -531,7 +527,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,15 +545,11 @@
           <t>07:14.137</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
+      <c r="G3" t="n">
+        <v>301</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -576,7 +568,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -621,7 +613,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -666,7 +658,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -711,7 +703,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -752,7 +744,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -770,15 +762,11 @@
           <t>08:48.706</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+      <c r="G8" t="n">
+        <v>236</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -797,7 +785,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -815,15 +803,11 @@
           <t>09:00.919</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="G9" t="n">
+        <v>249</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -842,7 +826,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -883,7 +867,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -928,7 +912,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1843342</v>
+        <v>2914333</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,29 +486,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sjors Beukeboom</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Gaul!</t>
-        </is>
-      </c>
+          <t xml:space="preserve">H  Sato </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06:48.434</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>355</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.6</v>
+          <t>06:34.993</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1265626</v>
+        <v>1843342</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -532,83 +532,83 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>Sjors Beukeboom</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>Gaul!</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07:14.137</t>
+          <t>06:48.434</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.703</t>
+          <t>13.441</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7533529</v>
+        <v>1979119</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
+          <t>Ruben Lammens (SPSD)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Sportsolid</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>07:14.538</t>
+          <t>06:51.982</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>16.989</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6627918</v>
+        <v>1265626</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -618,42 +618,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BL13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08:26.409</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>07:14.137</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>301</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>01:11.871</t>
+          <t>39.144</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7799511</v>
+        <v>7533529</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -663,7 +659,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -673,18 +669,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08:01.945</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
+          <t>07:14.538</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>387</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -694,93 +686,97 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5186335</v>
+        <v>2398750</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>S am (WMZ)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>16.208</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6784336</v>
+        <v>4738957</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08:48.706</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>236</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.8</v>
+          <t>07:37.076</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>22.538</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5609162</v>
+        <v>6627918</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -790,7 +786,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -800,24 +796,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>09:00.919</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>249</v>
+        <v>322</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>58.974</t>
+          <t>01:11.871</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7943676</v>
+        <v>7799511</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -831,38 +827,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09:24.744</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+          <t>08:01.945</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>397</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>679120</v>
+        <v>5186335</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -872,75 +868,309 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09:34.935</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+          <t>08:37.040</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>320</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>6784336</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Paul Fisk (TNP)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>08:48.706</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>236</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>46.761</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5609162</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Alan Robertson</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>09:00.919</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>249</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>58.974</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1267437</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>09:01.184</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>59.239</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7943676</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ed Henry</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>09:24.744</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>274</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>01:22.799</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>220793</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>11:06.763</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>03:04.818</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>237</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>1450582</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Phil Barthram</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Westbury Wheelers</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>11:37.609</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G18" t="n">
+        <v>219</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>02:02.674</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,15 +500,11 @@
           <t>06:34.993</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
+      <c r="G2" t="n">
+        <v>341</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -586,15 +582,11 @@
           <t>06:51.982</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
+      <c r="G4" t="n">
+        <v>364</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,15 +705,11 @@
           <t>07:30.746</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+      <c r="G7" t="n">
+        <v>358</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -754,15 +742,11 @@
           <t>07:37.076</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+      <c r="G8" t="n">
+        <v>353</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -813,48 +797,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7799511</v>
+        <v>3220143</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08:01.945</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>397</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.9</v>
+          <t>08:44.215</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:29.677</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5186335</v>
+        <v>7799511</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -868,30 +856,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6784336</v>
+        <v>5186335</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -905,34 +897,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5609162</v>
+        <v>6784336</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -946,7 +934,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -956,24 +944,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09:00.919</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>58.974</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -982,43 +970,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09:01.184</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
+          <t>09:00.919</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>249</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>58.974</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1027,35 +1011,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>220793</v>
+        <v>7943676</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1064,113 +1052,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11:06.763</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+          <t>09:24.744</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>274</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>679120</v>
+        <v>220793</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>237</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>53.284</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>1450582</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Phil Barthram</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Westbury Wheelers</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>11:37.609</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>219</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>2.4</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>02:02.674</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,48 +637,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7533529</v>
+        <v>2464931</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Mikkel Danielsen</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07:14.538</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>387</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.7</v>
+          <t>09:22.322</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:47.329</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2398750</v>
+        <v>7533529</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07:30.746</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.208</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4738957</v>
+        <v>2398750</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -733,30 +733,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>S am (WMZ)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H8" t="n">
         <v>4.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22.538</t>
+          <t>16.208</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6627918</v>
+        <v>4738957</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -765,39 +769,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:37.076</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>01:11.871</t>
+          <t>22.538</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3220143</v>
+        <v>6627918</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -806,84 +806,80 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08:44.215</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+          <t>08:26.409</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>322</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01:29.677</t>
+          <t>01:11.871</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7799511</v>
+        <v>3220143</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>397</v>
+        <v>301</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:29.677</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5186335</v>
+        <v>7799511</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -897,30 +893,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6784336</v>
+        <v>5186335</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -934,34 +934,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5609162</v>
+        <v>6784336</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -975,7 +971,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -985,24 +981,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09:00.919</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>58.974</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1011,39 +1007,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>09:00.919</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>58.974</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1052,35 +1048,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>220793</v>
+        <v>7943676</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1089,154 +1089,228 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>679120</v>
+        <v>220793</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6567346</v>
+        <v>4416917</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>53.284</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>237</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>172</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>53.284</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>1450582</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Phil Barthram</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Westbury Wheelers</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>11:37.609</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G22" t="n">
         <v>219</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H22" t="n">
         <v>2.4</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>02:02.674</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,15 +660,11 @@
           <t>09:22.322</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+      <c r="G6" t="n">
+        <v>268</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1177,15 +1173,11 @@
           <t>13:41.401</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+      <c r="G19" t="n">
+        <v>117</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1195,7 +1187,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>679120</v>
+        <v>5772535</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1204,29 +1196,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Derek Parrington</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>09:34.935</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>237</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.2</v>
+          <t>08:58.923</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1236,7 +1228,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6567346</v>
+        <v>7645137</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1250,69 +1242,319 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10:28.219</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>172</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.8</v>
+          <t>09:12.247</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>53.284</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>237</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>36.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>679358</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>09:43.353</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>44.430</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5863512</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>09:59.220</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>01:00.297</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>172</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:29.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>1450582</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Phil Barthram</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Westbury Wheelers</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>11:37.609</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G27" t="n">
         <v>219</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H27" t="n">
         <v>2.4</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>02:02.674</t>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1039041</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>J ester</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INOX</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>12:28.246</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>00.000</t>
         </is>
       </c>
     </row>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1265626</v>
+        <v>4606018</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -605,39 +605,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>John Lindestig [SZ]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>07:14.137</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>301</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.1</v>
+          <t>07:02.329</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>27.336</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2464931</v>
+        <v>1265626</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -646,76 +650,76 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mikkel Danielsen</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09:22.322</t>
+          <t>07:14.137</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>02:47.329</t>
+          <t>39.144</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7533529</v>
+        <v>2464931</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Mikkel Danielsen</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07:14.538</t>
+          <t>09:22.322</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>387</v>
+        <v>268</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:47.329</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2398750</v>
+        <v>7533529</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -724,39 +728,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07:30.746</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16.208</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4738957</v>
+        <v>2398750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,30 +774,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>S am (WMZ)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WMZ</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H9" t="n">
         <v>4.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.538</t>
+          <t>16.208</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6627918</v>
+        <v>4738957</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -802,39 +810,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:37.076</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01:11.871</t>
+          <t>22.538</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3220143</v>
+        <v>6627918</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -843,117 +847,125 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>01:29.677</t>
+          <t>01:11.871</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7799511</v>
+        <v>3220143</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>397</v>
+        <v>301</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:29.677</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5186335</v>
+        <v>5870438</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Steffen Dahlin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DZR</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08:37.040</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>320</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.7</v>
+          <t>09:01.783</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>01:47.245</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6784336</v>
+        <v>7799511</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -967,7 +979,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -977,24 +989,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>236</v>
+        <v>397</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5609162</v>
+        <v>5186335</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1008,34 +1020,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09:00.919</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.974</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1267437</v>
+        <v>6784336</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1044,39 +1052,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7943676</v>
+        <v>5609162</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1085,35 +1093,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Alan Robertson</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09:24.744</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>274</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.2</v>
+          <t>08:49.704</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>47.759</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>220793</v>
+        <v>1267437</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1127,30 +1143,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4416917</v>
+        <v>7943676</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1159,158 +1179,150 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5772535</v>
+        <v>6683056</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7645137</v>
+        <v>220793</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t xml:space="preserve">Gary James </t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09:12.247</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
+          <t>11:06.763</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>203</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>679120</v>
+        <v>4416917</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>237</v>
+        <v>117</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>679358</v>
+        <v>5772535</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1324,34 +1336,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
+          <t>Derek Parrington</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>09:43.353</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
+          <t>08:58.923</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>235</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5863512</v>
+        <v>7645137</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1365,34 +1373,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
+          <t>Marc Van Tol</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:59.220</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+          <t>09:12.247</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>309</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6567346</v>
+        <v>679120</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1401,39 +1405,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
+          <t>Fritz R.E.D. (63+)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>RSC OL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1789887</v>
+        <v>679358</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1447,34 +1451,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
+          <t>Steve Smith</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11:31.067</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
+          <t>09:43.353</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>264</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1450582</v>
+        <v>5863512</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1483,76 +1483,187 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>09:59.220</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>01:00.297</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>172</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>01:29.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>222</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>219</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>1039041</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="G31" t="n">
+        <v>195</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,15 +623,11 @@
           <t>07:02.329</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
+      <c r="G5" t="n">
+        <v>393</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6627918</v>
+        <v>7585082</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -847,39 +843,43 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08:26.409</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>322</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4</v>
+          <t>07:40.963</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>01:11.871</t>
+          <t>26.425</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3220143</v>
+        <v>6627918</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -888,39 +888,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:29.677</t>
+          <t>01:11.871</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5870438</v>
+        <v>3220143</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -934,79 +934,75 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09:01.783</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+          <t>08:44.215</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>301</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>01:47.245</t>
+          <t>01:29.677</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7799511</v>
+        <v>5870438</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>397</v>
+        <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:47.245</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5186335</v>
+        <v>7799511</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1020,30 +1016,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6784336</v>
+        <v>5186335</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1057,34 +1057,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5609162</v>
+        <v>6784336</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1093,12 +1089,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1108,28 +1104,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08:49.704</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
+          <t>08:48.706</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>236</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>47.759</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1143,34 +1135,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:49.704</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="H18" t="n">
         <v>3.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>47.759</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1179,35 +1171,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6683056</v>
+        <v>7943676</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1216,39 +1212,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10:12.916</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
+          <t>09:24.744</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>274</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>220793</v>
+        <v>6683056</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1262,30 +1254,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4416917</v>
+        <v>220793</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1299,67 +1291,67 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+          <t xml:space="preserve">Gary James </t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5772535</v>
+        <v>4416917</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>235</v>
+        <v>117</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7645137</v>
+        <v>5772535</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1373,30 +1365,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t>Derek Parrington</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>08:58.923</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="H24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>679120</v>
+        <v>7645137</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1405,39 +1397,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>09:12.247</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>679358</v>
+        <v>679120</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1446,35 +1434,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09:43.353</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5863512</v>
+        <v>679358</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1488,30 +1480,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
+          <t>Steve Smith</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>09:59.220</t>
+          <t>09:43.353</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6567346</v>
+        <v>5863512</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1525,34 +1517,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:59.220</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="H28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>01:00.297</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1789887</v>
+        <v>6567346</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1566,30 +1554,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>10:28.219</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="H29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>01:29.296</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1450582</v>
+        <v>1789887</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1598,72 +1590,109 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>11:31.067</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H30" t="n">
         <v>2.4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>02:32.144</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>219</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>1039041</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>195</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>2.2</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2914333</v>
+        <v>4508871</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,25 +486,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">H  Sato </t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Ken Van Staeyen</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BZR eCycling Club</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06:34.993</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>341</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.7</v>
+          <t>06:26.394</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -514,7 +522,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1843342</v>
+        <v>2914333</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -523,39 +531,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sjors Beukeboom</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Gaul!</t>
-        </is>
-      </c>
+          <t xml:space="preserve">H  Sato </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06:48.434</t>
+          <t>06:34.993</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13.441</t>
+          <t>08.599</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1979119</v>
+        <v>1843342</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -564,39 +568,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ruben Lammens (SPSD)</t>
+          <t>Sjors Beukeboom</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sportsolid</t>
+          <t>Gaul!</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>06:51.982</t>
+          <t>06:48.434</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.989</t>
+          <t>22.040</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4606018</v>
+        <v>1979119</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,34 +614,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>John Lindestig [SZ]</t>
+          <t>Ruben Lammens (SPSD)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>Sportsolid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>07:02.329</t>
+          <t>06:51.982</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27.336</t>
+          <t>25.588</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1265626</v>
+        <v>4606018</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -646,39 +650,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>John Lindestig [SZ]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07:14.137</t>
+          <t>07:02.329</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>301</v>
+        <v>393</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>35.935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2464931</v>
+        <v>1265626</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -687,39 +691,43 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mikkel Danielsen</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>09:22.322</t>
+          <t>07:14.137</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>02:47.329</t>
+          <t>47.743</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7533529</v>
+        <v>5218184</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -729,112 +737,120 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
+          <t>Chris Madge</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>EVOLVE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07:14.538</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>387</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.7</v>
+          <t>07:52.110</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:25.716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2398750</v>
+        <v>7255385</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
+          <t>Christoffer Collin [OUT]&amp;#128023;</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07:30.746</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>358</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.4</v>
+          <t>07:57.851</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.208</t>
+          <t>01:31.457</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4738957</v>
+        <v>2464931</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
+          <t>Mikkel Danielsen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>09:22.322</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.538</t>
+          <t>02:55.928</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7585082</v>
+        <v>502069</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -843,43 +859,43 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
+          <t>Giulio Cherubini (ITA-TTT)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07:40.963</t>
+          <t>06:53.513</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.425</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6627918</v>
+        <v>7533529</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -893,7 +909,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -903,24 +919,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:11.871</t>
+          <t>21.025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3220143</v>
+        <v>2398750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -934,34 +950,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>S am (WMZ)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>01:29.677</t>
+          <t>37.233</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5870438</v>
+        <v>4738957</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -975,79 +991,75 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DZR</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09:01.783</t>
+          <t>07:37.076</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>01:47.245</t>
+          <t>43.563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7799511</v>
+        <v>7585082</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>07:40.963</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>397</v>
+        <v>257</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>47.450</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5186335</v>
+        <v>6627918</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1057,112 +1069,116 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Liam Mckeever</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>01:32.896</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6784336</v>
+        <v>3220143</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>236</v>
+        <v>301</v>
       </c>
       <c r="H17" t="n">
         <v>3.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>01:50.702</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5609162</v>
+        <v>5870438</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08:49.704</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.759</t>
+          <t>02:08.270</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1267437</v>
+        <v>7799511</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1171,39 +1187,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>219</v>
+        <v>397</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7943676</v>
+        <v>5186335</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1217,30 +1233,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
+          <t>Nathan Smith</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6683056</v>
+        <v>6784336</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1249,35 +1265,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Paul Fisk (TNP)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10:12.916</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>220793</v>
+        <v>5609162</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1291,30 +1311,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Alan Robertson</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>08:49.704</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>47.759</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4416917</v>
+        <v>1267437</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1328,182 +1352,182 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>117</v>
+        <v>219</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5772535</v>
+        <v>7943676</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7645137</v>
+        <v>6683056</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>679120</v>
+        <v>220793</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>679358</v>
+        <v>4416917</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>09:43.353</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5863512</v>
+        <v>5772535</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1517,30 +1541,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
+          <t>Derek Parrington</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>09:59.220</t>
+          <t>08:58.923</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6567346</v>
+        <v>7645137</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1554,34 +1578,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:12.247</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="H29" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1789887</v>
+        <v>679120</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1590,35 +1610,39 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H30" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1450582</v>
+        <v>679358</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1627,72 +1651,269 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>09:43.353</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>5863512</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>09:59.220</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>212</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>01:00.297</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>172</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>01:29.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1635975</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Carsten Stark RSV-Erzgebirge e.V</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTB Erzgebirge </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11:12.983</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>02:14.060</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>222</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>219</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>1039041</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="G37" t="n">
         <v>195</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H37" t="n">
         <v>2.2</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,15 +504,11 @@
           <t>06:26.394</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
+      <c r="G2" t="n">
+        <v>402</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -750,15 +746,11 @@
           <t>07:52.110</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
+      <c r="G8" t="n">
+        <v>279</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -795,15 +787,11 @@
           <t>07:57.851</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
+      <c r="G9" t="n">
+        <v>331</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -877,15 +865,11 @@
           <t>06:53.513</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
+      <c r="G11" t="n">
+        <v>337</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1055,7 +1039,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6627918</v>
+        <v>5963960</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1064,39 +1048,43 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t>Sven Michael Hoelzl</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08:26.409</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>322</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
+          <t>07:49.459</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>01:32.896</t>
+          <t>55.946</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3220143</v>
+        <v>6627918</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1105,39 +1093,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>01:50.702</t>
+          <t>01:32.896</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5870438</v>
+        <v>3220143</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1151,75 +1139,75 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09:01.783</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>02:08.270</t>
+          <t>01:50.702</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7799511</v>
+        <v>5870438</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>397</v>
+        <v>263</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>02:08.270</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5186335</v>
+        <v>7799511</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1233,30 +1221,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6784336</v>
+        <v>5186335</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1270,34 +1262,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5609162</v>
+        <v>6784336</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1306,12 +1294,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1321,24 +1309,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08:49.704</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47.759</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1352,34 +1340,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:49.704</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="H23" t="n">
         <v>3.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>47.759</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1388,35 +1376,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6683056</v>
+        <v>7853567</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1430,30 +1422,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
+          <t>Pierre Puls</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10:12.916</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>244</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.9</v>
+          <t>09:07.563</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>01:05.618</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>220793</v>
+        <v>7943676</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1462,35 +1458,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4416917</v>
+        <v>6683056</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1504,104 +1500,104 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>117</v>
+        <v>244</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5772535</v>
+        <v>220793</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t xml:space="preserve">Gary James </t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="H28" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7645137</v>
+        <v>4416917</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>309</v>
+        <v>117</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>679120</v>
+        <v>5772535</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1610,39 +1606,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Derek Parrington</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>08:58.923</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>679358</v>
+        <v>7645137</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1656,30 +1648,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
+          <t>Marc Van Tol</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>09:43.353</t>
+          <t>09:12.247</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5863512</v>
+        <v>679120</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1688,35 +1680,39 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09:59.220</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6567346</v>
+        <v>679358</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1730,34 +1726,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:43.353</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>172</v>
+        <v>264</v>
       </c>
       <c r="H33" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1635975</v>
+        <v>5863512</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1766,43 +1758,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Carsten Stark RSV-Erzgebirge e.V</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MTB Erzgebirge </t>
-        </is>
-      </c>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11:12.983</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+          <t>09:59.220</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>212</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>02:14.060</t>
+          <t>01:00.297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1789887</v>
+        <v>6567346</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1816,30 +1800,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>10:28.219</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>01:29.296</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1450582</v>
+        <v>1635975</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1853,67 +1841,145 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
+          <t>Carsten Stark RSV-Erzgebirge e.V</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Westbury Wheelers</t>
+          <t xml:space="preserve">MTB Erzgebirge </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>11:12.983</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="H36" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>02:14.060</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>222</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>219</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>1039041</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G39" t="n">
         <v>195</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H39" t="n">
         <v>2.2</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -1066,15 +1066,11 @@
           <t>07:49.459</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+      <c r="G16" t="n">
+        <v>319</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1248,7 +1244,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5186335</v>
+        <v>5609162</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1257,35 +1253,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Alan Robertson</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08:37.040</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>320</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.7</v>
+          <t>08:29.316</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>27.371</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6784336</v>
+        <v>5186335</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1299,34 +1303,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Nathan Smith</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5609162</v>
+        <v>6784336</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1350,18 +1350,18 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>08:49.704</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>47.759</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
@@ -1431,15 +1431,11 @@
           <t>09:07.563</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="G25" t="n">
+        <v>288</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,7 +637,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4606018</v>
+        <v>429749</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -651,34 +651,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>John Lindestig [SZ]</t>
+          <t xml:space="preserve">Brage Bergeng [V] </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07:02.329</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>393</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.2</v>
+          <t>06:51.986</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.935</t>
+          <t>25.592</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1265626</v>
+        <v>4606018</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -687,39 +691,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>John Lindestig [SZ]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07:14.137</t>
+          <t>07:02.329</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>393</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.743</t>
+          <t>35.935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5218184</v>
+        <v>1265626</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -733,34 +737,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chris Madge</t>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>BL13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07:52.110</t>
+          <t>07:14.137</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>01:25.716</t>
+          <t>47.743</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7255385</v>
+        <v>493715</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -769,39 +773,43 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Christoffer Collin [OUT]&amp;#128023;</t>
+          <t>Jacob Kollerup | KST</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07:57.851</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>331</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.3</v>
+          <t>07:37.246</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>01:31.457</t>
+          <t>01:10.852</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2464931</v>
+        <v>5218184</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -810,39 +818,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mikkel Danielsen</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Chris Madge</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EVOLVE</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09:22.322</t>
+          <t>07:52.110</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>02:55.928</t>
+          <t>01:25.716</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>502069</v>
+        <v>7255385</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -852,116 +864,116 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Giulio Cherubini (ITA-TTT)</t>
+          <t>Christoffer Collin [OUT]&amp;#128023;</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06:53.513</t>
+          <t>07:57.851</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:31.457</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7533529</v>
+        <v>4829258</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
+          <t>Patrick S&amp;eacute;guin (Ride with Rendall) TT1D</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Lumberjacks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>07:14.538</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>387</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.7</v>
+          <t>08:05.269</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21.025</t>
+          <t>01:38.875</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2398750</v>
+        <v>2464931</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>WMZ</t>
-        </is>
-      </c>
+          <t>Mikkel Danielsen</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>07:30.746</t>
+          <t>09:22.322</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>358</v>
+        <v>268</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>37.233</t>
+          <t>02:55.928</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4738957</v>
+        <v>502069</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -970,35 +982,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Giulio Cherubini (ITA-TTT)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>06:53.513</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>43.563</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7585082</v>
+        <v>7533529</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1007,39 +1023,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>07:40.963</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>257</v>
+        <v>387</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.450</t>
+          <t>21.025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5963960</v>
+        <v>2398750</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1053,34 +1069,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sven Michael Hoelzl</t>
+          <t>S am (WMZ)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07:49.459</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="H16" t="n">
         <v>4.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>55.946</t>
+          <t>37.233</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6627918</v>
+        <v>4738957</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1089,39 +1105,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:37.076</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>01:32.896</t>
+          <t>43.563</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3220143</v>
+        <v>7585082</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1135,34 +1147,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>07:40.963</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>01:50.702</t>
+          <t>47.450</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5870438</v>
+        <v>5963960</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1176,124 +1188,128 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t>Sven Michael Hoelzl</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09:01.783</t>
+          <t>07:49.459</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>263</v>
+        <v>319</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>02:08.270</t>
+          <t>55.946</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7799511</v>
+        <v>4177429</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t xml:space="preserve">F F </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08:01.945</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>397</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.9</v>
+          <t>08:00.075</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:06.562</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5609162</v>
+        <v>1038506</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08:29.316</t>
+          <t>08:13.069</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27.371</t>
+          <t>01:19.556</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5186335</v>
+        <v>6627918</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1303,112 +1319,116 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Liam Mckeever</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>01:32.896</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6784336</v>
+        <v>3220143</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>236</v>
+        <v>301</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>01:50.702</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1267437</v>
+        <v>5870438</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>02:08.270</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7853567</v>
+        <v>7799511</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1417,35 +1437,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pierre Puls</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>B. Copestake</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09:07.563</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>288</v>
+        <v>397</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>01:05.618</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7943676</v>
+        <v>21341</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1454,35 +1478,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Michiel van der Wal [BEAT]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BEAT</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09:24.744</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>274</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.2</v>
+          <t>08:14.519</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>12.574</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6683056</v>
+        <v>5609162</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1496,30 +1528,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Alan Robertson</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10:12.916</t>
+          <t>08:29.316</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>27.371</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>220793</v>
+        <v>5186335</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1528,35 +1564,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
+          <t>Nathan Smith</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4416917</v>
+        <v>3449821</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1570,412 +1606,822 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>Chris Cook (ART)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ART</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13:41.401</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>117</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.2</v>
+          <t>08:44.061</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>42.116</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5772535</v>
+        <v>6784336</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Paul Fisk (TNP)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7645137</v>
+        <v>1267437</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>309</v>
+        <v>219</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>679120</v>
+        <v>7853567</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t>Pierre Puls</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>09:07.563</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>01:05.618</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>679358</v>
+        <v>39415</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>Greg Lewis (OTR)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>09:43.353</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>264</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.1</v>
+          <t>09:09.271</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>01:07.326</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5863512</v>
+        <v>3084196</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09:59.220</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>212</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
+          <t>09:10.644</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>01:08.699</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6567346</v>
+        <v>7943676</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Ed Henry</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>172</v>
+        <v>274</v>
       </c>
       <c r="H35" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1635975</v>
+        <v>6683056</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Carsten Stark RSV-Erzgebirge e.V</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MTB Erzgebirge </t>
-        </is>
-      </c>
+          <t>Bryan Zhang</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11:12.983</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>199</v>
+        <v>244</v>
       </c>
       <c r="H36" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>02:14.060</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1789887</v>
+        <v>220793</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
+          <t xml:space="preserve">Gary James </t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="H37" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1450582</v>
+        <v>4416917</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="H38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>5772535</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Derek Parrington</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>08:58.923</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>235</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7645137</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>09:12.247</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>309</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>13.324</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>679120</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>09:34.935</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>237</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>36.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>679358</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>09:43.353</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>264</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>44.430</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5863512</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>09:59.220</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>212</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>01:00.297</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>172</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>01:29.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1635975</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Carsten Stark RSV-Erzgebirge e.V</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTB Erzgebirge </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11:12.983</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>199</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>02:14.060</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>222</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>219</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1117319</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fco Ripoll </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PETA-Z</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>11:44.362</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02:45.439</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>1039041</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="G49" t="n">
         <v>195</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H49" t="n">
         <v>2.2</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1843342</v>
+        <v>1959892</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -564,39 +564,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sjors Beukeboom</t>
+          <t>Gavin Lancaster (PDQ RT) VTTA 16004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gaul!</t>
+          <t>PDQ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>06:48.434</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>355</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.6</v>
+          <t>06:45.548</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.040</t>
+          <t>19.154</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1979119</v>
+        <v>1843342</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -605,39 +609,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ruben Lammens (SPSD)</t>
+          <t>Sjors Beukeboom</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sportsolid</t>
+          <t>Gaul!</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06:51.982</t>
+          <t>06:48.434</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25.588</t>
+          <t>22.040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>429749</v>
+        <v>1979119</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -651,38 +655,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brage Bergeng [V] </t>
+          <t>Ruben Lammens (SPSD)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>Sportsolid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06:51.986</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
+          <t>06:51.982</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>364</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.592</t>
+          <t>25.588</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4606018</v>
+        <v>429749</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -696,34 +696,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>John Lindestig [SZ]</t>
+          <t xml:space="preserve">Brage Bergeng [V] </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07:02.329</t>
+          <t>06:51.986</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35.935</t>
+          <t>25.592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1265626</v>
+        <v>1511742</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -732,39 +732,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07:14.137</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>301</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.1</v>
+          <t>07:01.755</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47.743</t>
+          <t>35.361</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>493715</v>
+        <v>4606018</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -778,38 +782,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jacob Kollerup | KST</t>
+          <t>John Lindestig [SZ]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07:37.246</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+          <t>07:02.329</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>393</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>01:10.852</t>
+          <t>35.935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5218184</v>
+        <v>1265626</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -823,34 +823,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chris Madge</t>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>BL13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07:52.110</t>
+          <t>07:14.137</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01:25.716</t>
+          <t>47.743</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7255385</v>
+        <v>7104670</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -859,39 +859,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Christoffer Collin [OUT]&amp;#128023;</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
+          <t>Hisashi Nishikawa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07:57.851</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>331</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.3</v>
+          <t>07:21.221</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>01:31.457</t>
+          <t>54.827</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4829258</v>
+        <v>493715</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -905,38 +905,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Patrick S&amp;eacute;guin (Ride with Rendall) TT1D</t>
+          <t>Jacob Kollerup | KST</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lumberjacks</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08:05.269</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
+          <t>07:37.246</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>315</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:38.875</t>
+          <t>01:10.852</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2464931</v>
+        <v>772499</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -950,34 +946,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mikkel Danielsen</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>T Ired (DIRTy Rascals Rogue)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09:22.322</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>268</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.8</v>
+          <t>07:38.446</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>02:55.928</t>
+          <t>01:12.052</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>502069</v>
+        <v>5218184</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -987,38 +991,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Giulio Cherubini (ITA-TTT)</t>
+          <t>Chris Madge</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>EVOLVE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06:53.513</t>
+          <t>07:52.110</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>337</v>
+        <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:25.716</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7533529</v>
+        <v>7255385</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1028,112 +1032,112 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
+          <t>Christoffer Collin [OUT]&amp;#128023;</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>07:14.538</t>
+          <t>07:57.851</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.025</t>
+          <t>01:31.457</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2398750</v>
+        <v>4829258</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
+          <t>Patrick S&amp;eacute;guin (Ride with Rendall) TT1D</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>Lumberjacks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07:30.746</t>
+          <t>08:05.269</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.233</t>
+          <t>01:38.875</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4738957</v>
+        <v>2464931</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
+          <t>Mikkel Danielsen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>09:22.322</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43.563</t>
+          <t>02:55.928</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7585082</v>
+        <v>502069</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1142,39 +1146,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
+          <t>Giulio Cherubini (ITA-TTT)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07:40.963</t>
+          <t>06:53.513</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>257</v>
+        <v>337</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.450</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5963960</v>
+        <v>7533529</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1183,39 +1187,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sven Michael Hoelzl</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07:49.459</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>319</v>
+        <v>387</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>55.946</t>
+          <t>21.025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4177429</v>
+        <v>2398750</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1229,38 +1233,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
+          <t>S am (WMZ)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08:00.075</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+          <t>07:30.746</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>358</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>01:06.562</t>
+          <t>37.233</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1038506</v>
+        <v>4738957</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1274,38 +1274,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Vikings</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08:13.069</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
+          <t>07:37.076</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>353</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>01:19.556</t>
+          <t>43.563</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6627918</v>
+        <v>7585082</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1314,39 +1306,39 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:40.963</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>322</v>
+        <v>257</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>01:32.896</t>
+          <t>47.450</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3220143</v>
+        <v>5963960</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1360,34 +1352,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t>Sven Michael Hoelzl</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>07:49.459</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>01:50.702</t>
+          <t>55.946</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5870438</v>
+        <v>4177429</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1401,198 +1393,198 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t xml:space="preserve">F F </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:01.783</t>
+          <t>08:00.075</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>02:08.270</t>
+          <t>01:06.562</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7799511</v>
+        <v>1038506</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>08:13.069</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>397</v>
+        <v>243</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:19.556</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21341</v>
+        <v>6627918</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Michiel van der Wal [BEAT]</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BEAT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08:14.519</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
+          <t>08:26.409</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>322</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12.574</t>
+          <t>01:32.896</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5609162</v>
+        <v>3220143</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08:29.316</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27.371</t>
+          <t>01:50.702</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5186335</v>
+        <v>5870438</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>Steffen Dahlin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DZR</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>08:37.040</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>320</v>
+        <v>263</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>02:08.270</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3449821</v>
+        <v>7799511</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1601,43 +1593,39 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chris Cook (ART)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ART</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08:44.061</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
+          <t>08:01.945</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>397</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>42.116</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6784336</v>
+        <v>21341</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1646,39 +1634,39 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>Michiel van der Wal [BEAT]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BEAT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:14.519</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="H30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>12.574</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1692,34 +1680,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:29.316</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>27.371</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7853567</v>
+        <v>5186335</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1728,35 +1716,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pierre Puls</t>
+          <t>Nathan Smith</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09:07.563</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01:05.618</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>39415</v>
+        <v>3449821</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1770,38 +1758,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Greg Lewis (OTR)</t>
+          <t>Chris Cook (ART)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>ART</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>09:09.271</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+          <t>08:44.061</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>312</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>01:07.326</t>
+          <t>42.116</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3084196</v>
+        <v>6784336</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1810,43 +1794,39 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darin Mills </t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09:10.644</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
+          <t>08:48.706</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>236</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>01:08.699</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1855,35 +1835,39 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6683056</v>
+        <v>7853567</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1897,30 +1881,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
+          <t>Pierre Puls</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10:12.916</t>
+          <t>09:07.563</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="H36" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>01:05.618</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>220793</v>
+        <v>39415</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1934,30 +1918,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>Greg Lewis (OTR)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>09:09.271</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="H37" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>01:07.326</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4416917</v>
+        <v>3084196</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1971,182 +1959,182 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>09:10.644</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="H38" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>01:08.699</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5772535</v>
+        <v>7943676</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7645137</v>
+        <v>6683056</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>679120</v>
+        <v>220793</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>679358</v>
+        <v>4416917</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>09:43.353</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5863512</v>
+        <v>5772535</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2160,30 +2148,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
+          <t>Derek Parrington</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>09:59.220</t>
+          <t>08:58.923</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6567346</v>
+        <v>7645137</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2197,34 +2185,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>09:12.247</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="H44" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1635975</v>
+        <v>679120</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2238,34 +2222,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Carsten Stark RSV-Erzgebirge e.V</t>
+          <t>Fritz R.E.D. (63+)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTB Erzgebirge </t>
+          <t>RSC OL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>11:12.983</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>02:14.060</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1789887</v>
+        <v>679358</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2279,30 +2263,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
+          <t>Steve Smith</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>09:43.353</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="H46" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1450582</v>
+        <v>5863512</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2311,39 +2295,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>09:59.220</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H47" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>01:00.297</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1117319</v>
+        <v>6567346</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2357,71 +2337,227 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fco Ripoll </t>
+          <t>Jill Wood [GXY]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PETA-Z</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>11:44.362</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>172</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>02:45.439</t>
+          <t>01:29.296</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>1635975</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Carsten Stark RSV-Erzgebirge e.V</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTB Erzgebirge </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>11:12.983</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>199</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>02:14.060</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>222</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>219</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1117319</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fco Ripoll </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PETA-Z</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>11:44.362</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>160</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>02:45.439</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
         <v>1039041</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="G53" t="n">
         <v>195</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H53" t="n">
         <v>2.2</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,15 +582,11 @@
           <t>06:45.548</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
+      <c r="G4" t="n">
+        <v>407</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -750,15 +746,11 @@
           <t>07:01.755</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
+      <c r="G8" t="n">
+        <v>335</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -809,7 +801,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1265626</v>
+        <v>5283167</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -818,39 +810,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+          <t>Jeppe AV Thomsen [eCKD]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>eCKD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07:14.137</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>301</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5.1</v>
+          <t>07:10.519</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>47.743</t>
+          <t>44.125</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7104670</v>
+        <v>1265626</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -859,39 +855,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hisashi Nishikawa</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t xml:space="preserve">Alex Stuart r (BL13) </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BL13</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07:21.221</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
+          <t>07:14.137</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>301</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>54.827</t>
+          <t>47.743</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>493715</v>
+        <v>174373</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -905,34 +901,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jacob Kollerup | KST</t>
+          <t xml:space="preserve">Louis Prins (SqAzBi) </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KST</t>
+          <t>SqAzBi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>07:37.246</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>315</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.4</v>
+          <t>07:17.853</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:10.852</t>
+          <t>51.459</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>772499</v>
+        <v>7104670</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -946,38 +946,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T Ired (DIRTy Rascals Rogue)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Hisashi Nishikawa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>07:38.446</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
+          <t>07:21.221</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>304</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>01:12.052</t>
+          <t>54.827</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5218184</v>
+        <v>493715</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -986,39 +978,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chris Madge</t>
+          <t>Jacob Kollerup | KST</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>KST</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>07:52.110</t>
+          <t>07:37.246</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>01:25.716</t>
+          <t>01:10.852</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7255385</v>
+        <v>772499</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1027,39 +1019,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Christoffer Collin [OUT]&amp;#128023;</t>
+          <t>T Ired (DIRTy Rascals Rogue)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>07:57.851</t>
+          <t>07:38.446</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>331</v>
+        <v>246</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>01:31.457</t>
+          <t>01:12.052</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4829258</v>
+        <v>5218184</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1068,39 +1060,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Patrick S&amp;eacute;guin (Ride with Rendall) TT1D</t>
+          <t>Chris Madge</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumberjacks</t>
+          <t>EVOLVE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08:05.269</t>
+          <t>07:52.110</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="H16" t="n">
         <v>4.3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>01:38.875</t>
+          <t>01:25.716</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2464931</v>
+        <v>7255385</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1109,158 +1101,162 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mikkel Danielsen</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Christoffer Collin [OUT]&amp;#128023;</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09:22.322</t>
+          <t>07:57.851</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>02:55.928</t>
+          <t>01:31.457</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>502069</v>
+        <v>4829258</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Giulio Cherubini (ITA-TTT)</t>
+          <t>Patrick S&amp;eacute;guin (Ride with Rendall) TT1D</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>Lumberjacks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06:53.513</t>
+          <t>08:05.269</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:38.875</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7533529</v>
+        <v>2464931</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Mikkel Danielsen</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07:14.538</t>
+          <t>09:22.322</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>387</v>
+        <v>268</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.025</t>
+          <t>02:55.928</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2398750</v>
+        <v>1996391</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>S am (WMZ)</t>
+          <t xml:space="preserve">#AzorCabral </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WMZ</t>
+          <t>FxCancerTeam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>07:30.746</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>358</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.4</v>
+          <t>14:04.394</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37.233</t>
+          <t>07:38.000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4738957</v>
+        <v>502069</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1269,35 +1265,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Markus Jochimsen</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Giulio Cherubini (ITA-TTT)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>07:37.076</t>
+          <t>06:53.513</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>43.563</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7585082</v>
+        <v>7533529</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1306,39 +1306,39 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>&amp;#128123; Ghost &amp;#128123;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>07:40.963</t>
+          <t>07:14.538</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>257</v>
+        <v>387</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47.450</t>
+          <t>21.025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5963960</v>
+        <v>2398750</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1352,34 +1352,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sven Michael Hoelzl</t>
+          <t>S am (WMZ)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>WMZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>07:49.459</t>
+          <t>07:30.746</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>55.946</t>
+          <t>37.233</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4177429</v>
+        <v>4738957</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1393,34 +1393,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">F F </t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>L&amp;rsquo;Equipe Provence</t>
-        </is>
-      </c>
+          <t>Markus Jochimsen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>08:00.075</t>
+          <t>07:37.076</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>194</v>
+        <v>353</v>
       </c>
       <c r="H24" t="n">
         <v>4.4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01:06.562</t>
+          <t>43.563</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1038506</v>
+        <v>7585082</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1434,34 +1430,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
+          <t>A  fondv&amp;eacute;lo! [Ghost]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vikings</t>
+          <t>&amp;#128123; Ghost &amp;#128123;</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08:13.069</t>
+          <t>07:40.963</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>01:19.556</t>
+          <t>47.450</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6627918</v>
+        <v>5963960</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1470,39 +1466,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Liam Mckeever</t>
+          <t>Sven Michael Hoelzl</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08:26.409</t>
+          <t>07:49.459</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>01:32.896</t>
+          <t>55.946</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3220143</v>
+        <v>4177429</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1516,34 +1512,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Derek Sheridan (IRL DS1)</t>
+          <t xml:space="preserve">F F </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>L&amp;rsquo;Equipe Provence</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08:44.215</t>
+          <t>08:00.075</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>301</v>
+        <v>194</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>01:50.702</t>
+          <t>01:06.562</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5870438</v>
+        <v>1038506</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1557,38 +1553,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Steffen Dahlin</t>
+          <t xml:space="preserve">Anne  L&amp;oslash;fshus [V] </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DZR</t>
+          <t>Vikings</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>09:01.783</t>
+          <t>08:13.069</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="H28" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>02:08.270</t>
+          <t>01:19.556</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7799511</v>
+        <v>6627918</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1598,7 +1594,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Liam Mckeever</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1608,143 +1604,151 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08:01.945</t>
+          <t>08:26.409</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>397</v>
+        <v>322</v>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:32.896</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21341</v>
+        <v>3220143</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Michiel van der Wal [BEAT]</t>
+          <t>Derek Sheridan (IRL DS1)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BEAT</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>08:14.519</t>
+          <t>08:44.215</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12.574</t>
+          <t>01:50.702</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5609162</v>
+        <v>5870438</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Steffen Dahlin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>DZR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>08:29.316</t>
+          <t>09:01.783</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="H31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27.371</t>
+          <t>02:08.270</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5186335</v>
+        <v>842196</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nathan Smith</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Daniel J&amp;ouml;nsson [SZR]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SZR</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>08:37.040</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>320</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.7</v>
+          <t>11:46.097</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>04:52.584</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3449821</v>
+        <v>7799511</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1753,39 +1757,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Chris Cook (ART)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ART</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>08:44.061</t>
+          <t>08:01.945</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>312</v>
+        <v>397</v>
       </c>
       <c r="H33" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>42.116</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6784336</v>
+        <v>21341</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1794,39 +1798,39 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paul Fisk (TNP)</t>
+          <t>Michiel van der Wal [BEAT]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BEAT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>08:48.706</t>
+          <t>08:14.519</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="H34" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>46.761</t>
+          <t>12.574</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1267437</v>
+        <v>5609162</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1840,34 +1844,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Vincent de brackeleer</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>09:01.184</t>
+          <t>08:29.316</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>59.239</t>
+          <t>27.371</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7853567</v>
+        <v>5186335</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1876,35 +1880,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pierre Puls</t>
+          <t>Nathan Smith</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>09:07.563</t>
+          <t>08:37.040</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>01:05.618</t>
+          <t>35.095</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>39415</v>
+        <v>3449821</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1918,34 +1922,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Greg Lewis (OTR)</t>
+          <t>Chris Cook (ART)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>ART</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>09:09.271</t>
+          <t>08:44.061</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="H37" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>01:07.326</t>
+          <t>42.116</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3084196</v>
+        <v>6784336</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1954,39 +1958,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darin Mills </t>
+          <t>Paul Fisk (TNP)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>09:10.644</t>
+          <t>08:48.706</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="H38" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>01:08.699</t>
+          <t>46.761</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7943676</v>
+        <v>1267437</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1995,35 +1999,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ed Henry</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Vincent de brackeleer</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>09:24.744</t>
+          <t>09:01.184</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>01:22.799</t>
+          <t>59.239</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6683056</v>
+        <v>7853567</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2037,30 +2045,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bryan Zhang</t>
+          <t>Pierre Puls</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10:12.916</t>
+          <t>09:07.563</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="H40" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>02:10.971</t>
+          <t>01:05.618</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>220793</v>
+        <v>39415</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2074,30 +2082,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gary James </t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Greg Lewis (OTR)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11:06.763</t>
+          <t>09:09.271</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>03:04.818</t>
+          <t>01:07.326</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4416917</v>
+        <v>3084196</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2111,219 +2123,227 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t xml:space="preserve">Darin Mills </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13:41.401</t>
+          <t>09:10.644</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="H42" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>05:39.456</t>
+          <t>01:08.699</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5772535</v>
+        <v>7943676</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Derek Parrington</t>
+          <t>Ed Henry</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>08:58.923</t>
+          <t>09:24.744</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="H43" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:22.799</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7645137</v>
+        <v>6683056</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Marc Van Tol</t>
+          <t>Bryan Zhang</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>09:12.247</t>
+          <t>10:12.916</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="H44" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>13.324</t>
+          <t>02:10.971</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>679120</v>
+        <v>220793</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fritz R.E.D. (63+)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RSC OL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gary James </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>09:34.935</t>
+          <t>11:06.763</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="H45" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>36.012</t>
+          <t>03:04.818</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>679358</v>
+        <v>1421909</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Steve Smith</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>Aaron Derdowski</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>09:43.353</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>264</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.1</v>
+          <t>11:41.061</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>44.430</t>
+          <t>03:39.116</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5863512</v>
+        <v>4416917</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Frederick Sandro</t>
+          <t>Masaka Cycling Club MCCF2 (MASAKA)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>09:59.220</t>
+          <t>13:41.401</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>01:00.297</t>
+          <t>05:39.456</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6567346</v>
+        <v>5772535</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2337,34 +2357,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jill Wood [GXY]</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Derek Parrington</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10:28.219</t>
+          <t>08:58.923</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="H48" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>01:29.296</t>
+          <t>00.000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1635975</v>
+        <v>7645137</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2373,39 +2389,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Carsten Stark RSV-Erzgebirge e.V</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MTB Erzgebirge </t>
-        </is>
-      </c>
+          <t>Marc Van Tol</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>11:12.983</t>
+          <t>09:12.247</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="H49" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>02:14.060</t>
+          <t>13.324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1789887</v>
+        <v>679120</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2414,35 +2426,39 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gianluca Bergamaschi</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Fritz R.E.D. (63+)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RSC OL</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>11:31.067</t>
+          <t>09:34.935</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H50" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>02:32.144</t>
+          <t>36.012</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1450582</v>
+        <v>679358</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2451,39 +2467,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Phil Barthram</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Westbury Wheelers</t>
-        </is>
-      </c>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>11:37.609</t>
+          <t>09:43.353</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="H51" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>02:38.686</t>
+          <t>44.430</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1117319</v>
+        <v>5863512</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2497,67 +2509,264 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fco Ripoll </t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>PETA-Z</t>
-        </is>
-      </c>
+          <t>Frederick Sandro</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>11:44.362</t>
+          <t>09:59.220</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="H52" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>02:45.439</t>
+          <t>01:00.297</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>6567346</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jill Wood [GXY]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10:28.219</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>172</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>01:29.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1635975</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Carsten Stark RSV-Erzgebirge e.V</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MTB Erzgebirge </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>11:12.983</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>199</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>02:14.060</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1789887</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Gianluca Bergamaschi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>11:31.067</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>222</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>02:32.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1450582</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Phil Barthram</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Westbury Wheelers</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>11:37.609</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>219</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>02:38.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1117319</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fco Ripoll </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PETA-Z</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>11:44.362</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>160</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>02:45.439</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
         <v>1039041</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>J ester</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>INOX</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>12:28.246</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G58" t="n">
         <v>195</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H58" t="n">
         <v>2.2</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>

--- a/PowerTest/PowerTest.xlsx
+++ b/PowerTest/PowerTest.xlsx
@@ -828,15 +828,11 @@
           <t>07:10.519</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+      <c r="G10" t="n">
+        <v>376</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -914,15 +910,11 @@
           <t>07:17.853</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
+      <c r="G12" t="n">
+        <v>342</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1238,15 +1230,11 @@
           <t>14:04.394</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
+      <c r="G20" t="n">
+        <v>154</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1730,15 +1718,11 @@
           <t>11:46.097</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="G32" t="n">
+        <v>180</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2288,15 +2272,11 @@
           <t>11:41.061</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
+      <c r="G46" t="n">
+        <v>174</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
